--- a/StructureDefinition-inera-ehds-provenance.xlsx
+++ b/StructureDefinition-inera-ehds-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t>Tidpunkt för dokumentation (documentTime från RIVTA, UTC ISO 8601)</t>
+    <t>Tidpunkt för dokumentation (documentTime från RIVTA, UTC ISO 8601). OBS: för TK:er där documentTime har kardinalitet 0..0 (t.ex. GetDiagnosis) används istället accountableHealthcareProfessional.authorTime – se tjänstekontraktets mappningssida</t>
   </si>
   <si>
     <t>The instant of time at which the activity was recorded.</t>

--- a/StructureDefinition-inera-ehds-provenance.xlsx
+++ b/StructureDefinition-inera-ehds-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-provenance.xlsx
+++ b/StructureDefinition-inera-ehds-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t>Tidpunkt för dokumentation (documentTime från RIVTA, UTC ISO 8601). OBS: för TK:er där documentTime har kardinalitet 0..0 (t.ex. GetDiagnosis) används istället accountableHealthcareProfessional.authorTime – se tjänstekontraktets mappningssida</t>
+    <t>Tidpunkt för dokumentation (documentTime från RIVTA, UTC ISO 8601). OBS: för TK:er där documentTime har kardinalitet 0..0 (t.ex. GetDiagnosis) används istället accountableHealthcareProfessional.authorTime; för GetCareDocumentation (JoL-header) används header.author.timestamp med fallback header.record.timestamp (DOC-002) – se tjänstekontraktets mappningssida</t>
   </si>
   <si>
     <t>The instant of time at which the activity was recorded.</t>

--- a/StructureDefinition-inera-ehds-provenance.xlsx
+++ b/StructureDefinition-inera-ehds-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t>Tidpunkt för dokumentation (documentTime från RIVTA, UTC ISO 8601). OBS: för TK:er där documentTime har kardinalitet 0..0 (t.ex. GetDiagnosis) används istället accountableHealthcareProfessional.authorTime; för GetCareDocumentation (JoL-header) används header.author.timestamp med fallback header.record.timestamp (DOC-002) – se tjänstekontraktets mappningssida</t>
+    <t>Tidpunkt för dokumentation (documentTime från RIVTA, tolkad som Europe/Stockholm och angiven med offset, se GENERAL-001). OBS: för TK:er där documentTime har kardinalitet 0..0 (t.ex. GetDiagnosis) används istället accountableHealthcareProfessional.authorTime; för GetCareDocumentation (JoL-header) används header.author.timestamp med fallback header.record.timestamp (DOC-002) – se tjänstekontraktets mappningssida</t>
   </si>
   <si>
     <t>The instant of time at which the activity was recorded.</t>
